--- a/data/dividends_info_20261013.xlsx
+++ b/data/dividends_info_20261013.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>43.93000030517578</v>
+        <v>43.83499908447266</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2048713848731667</v>
+        <v>0.2053153915358014</v>
       </c>
       <c r="J2" t="n">
         <v>153</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>61.90000152587891</v>
+        <v>61.79999923706055</v>
       </c>
       <c r="I3" t="n">
-        <v>1.130856191832801</v>
+        <v>1.132686098125743</v>
       </c>
       <c r="J3" t="n">
         <v>132</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.760000228881836</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6849314889533816</v>
+        <v>0.674157332266361</v>
       </c>
       <c r="J4" t="n">
         <v>62</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43.93500137329102</v>
+        <v>43.83499908447266</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2048480646109933</v>
+        <v>0.2053153915358014</v>
       </c>
       <c r="J6" t="n">
         <v>62</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.039999961853027</v>
+        <v>2.045000076293945</v>
       </c>
       <c r="I7" t="n">
-        <v>3.774509874503002</v>
+        <v>3.765281033120711</v>
       </c>
       <c r="J7" t="n">
         <v>41</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>49.91999816894531</v>
+        <v>50.25</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6209936125214998</v>
+        <v>0.6169154228855721</v>
       </c>
       <c r="J8" t="n">
         <v>41</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>25.58499908447266</v>
+        <v>25.67000007629395</v>
       </c>
       <c r="I9" t="n">
-        <v>1.055305881030346</v>
+        <v>1.05181144993195</v>
       </c>
       <c r="J9" t="n">
         <v>41</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>26.13999938964844</v>
+        <v>26.01000022888184</v>
       </c>
       <c r="I10" t="n">
-        <v>2.257077328906299</v>
+        <v>2.26835830376063</v>
       </c>
       <c r="J10" t="n">
         <v>41</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11.31999969482422</v>
+        <v>11.11999988555908</v>
       </c>
       <c r="I11" t="n">
-        <v>1.855123724923925</v>
+        <v>1.888489228068385</v>
       </c>
       <c r="J11" t="n">
         <v>34</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.849999904632568</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I13" t="n">
-        <v>1.196581216088013</v>
+        <v>1.206896512034959</v>
       </c>
       <c r="J13" t="n">
         <v>27</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8.060000419616699</v>
+        <v>8.029999732971191</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7444168346935812</v>
+        <v>0.7471980323192279</v>
       </c>
       <c r="J14" t="n">
         <v>27</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.77999973297119</v>
+        <v>10.73999977111816</v>
       </c>
       <c r="I15" t="n">
-        <v>4.267161515719393</v>
+        <v>4.283054095001237</v>
       </c>
       <c r="J15" t="n">
         <v>13</v>
@@ -1180,8 +1180,12 @@
           <t>IT0005359101</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>8.449999809265137</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.710059187625212</v>
+      </c>
       <c r="J16" t="n">
         <v>6</v>
       </c>
@@ -1271,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3.880000114440918</v>
+        <v>3.890000104904175</v>
       </c>
       <c r="I18" t="n">
-        <v>1.288659755805308</v>
+        <v>1.285347009039006</v>
       </c>
       <c r="J18" t="n">
         <v>-8</v>
@@ -1318,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7.940000057220459</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="I19" t="n">
-        <v>0.478589417205906</v>
+        <v>0.4810126524211467</v>
       </c>
       <c r="J19" t="n">
         <v>-15</v>
@@ -1365,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>25.58499908447266</v>
+        <v>25.67000007629395</v>
       </c>
       <c r="I20" t="n">
-        <v>1.055305881030346</v>
+        <v>1.05181144993195</v>
       </c>
       <c r="J20" t="n">
         <v>-22</v>
@@ -1412,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.909000039100647</v>
+        <v>1.922000050544739</v>
       </c>
       <c r="I21" t="n">
-        <v>2.985856408198577</v>
+        <v>2.965660692040299</v>
       </c>
       <c r="J21" t="n">
         <v>-22</v>
@@ -1459,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>43.93500137329102</v>
+        <v>43.83499908447266</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2048480646109933</v>
+        <v>0.2053153915358014</v>
       </c>
       <c r="J22" t="n">
         <v>-22</v>
@@ -1506,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>94.80000305175781</v>
+        <v>94.90000152587891</v>
       </c>
       <c r="I23" t="n">
-        <v>1.402953541334658</v>
+        <v>1.401475214557624</v>
       </c>
       <c r="J23" t="n">
         <v>-22</v>
@@ -1553,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5.559999942779541</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I24" t="n">
-        <v>5.395683508766814</v>
+        <v>5.263158070853988</v>
       </c>
       <c r="J24" t="n">
         <v>-29</v>
@@ -1667,7 +1671,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1684,7 +1688,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1701,7 +1705,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1711,14 +1715,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1728,14 +1732,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1745,14 +1749,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1762,14 +1766,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1779,14 +1783,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1796,14 +1800,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1813,14 +1817,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1830,14 +1834,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1847,14 +1851,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1864,14 +1868,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1881,14 +1885,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1905,7 +1909,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1922,7 +1926,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1939,7 +1943,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1949,14 +1953,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1966,14 +1970,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1990,7 +1994,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2000,14 +2004,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2024,7 +2028,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2034,14 +2038,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2051,14 +2055,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2075,7 +2079,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2085,14 +2089,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2177,7 +2181,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2194,7 +2198,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2211,7 +2215,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2228,7 +2232,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2245,7 +2249,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2262,7 +2266,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2272,14 +2276,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2289,14 +2293,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2306,14 +2310,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2330,7 +2334,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2340,14 +2344,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2364,7 +2368,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2374,7 +2378,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2391,14 +2395,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2408,14 +2412,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2432,7 +2436,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2442,14 +2446,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2534,7 +2538,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2731,14 +2735,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2748,14 +2752,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2772,7 +2776,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2857,7 +2861,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2874,7 +2878,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2891,7 +2895,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2925,7 +2929,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2942,7 +2946,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2952,14 +2956,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2969,14 +2973,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3010,7 +3014,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3061,7 +3065,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3129,7 +3133,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3156,14 +3160,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3173,14 +3177,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3190,7 +3194,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3207,14 +3211,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3248,7 +3252,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3384,7 +3388,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3401,7 +3405,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3411,14 +3415,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3435,7 +3439,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3445,14 +3449,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3462,14 +3466,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3486,7 +3490,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3503,7 +3507,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3520,7 +3524,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3537,7 +3541,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3554,7 +3558,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3571,7 +3575,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3581,14 +3585,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3605,7 +3609,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3622,7 +3626,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3632,14 +3636,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3656,7 +3660,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3666,14 +3670,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3690,7 +3694,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3707,7 +3711,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3741,7 +3745,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3751,7 +3755,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3779,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3785,14 +3789,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3802,14 +3806,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3819,14 +3823,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3843,7 +3847,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3853,14 +3857,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3870,14 +3874,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3887,14 +3891,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3911,7 +3915,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3921,14 +3925,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3945,7 +3949,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3962,7 +3966,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3972,7 +3976,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3993,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4017,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4030,7 +4034,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4040,14 +4044,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4064,7 +4068,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4074,14 +4078,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4098,7 +4102,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4108,14 +4112,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4132,7 +4136,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4142,14 +4146,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4159,14 +4163,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4176,14 +4180,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4200,7 +4204,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4217,7 +4221,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4234,7 +4238,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4244,14 +4248,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4268,7 +4272,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4278,14 +4282,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4302,7 +4306,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4312,14 +4316,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4336,7 +4340,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4346,14 +4350,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4363,14 +4367,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4387,7 +4391,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4404,7 +4408,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4421,7 +4425,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4431,14 +4435,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4455,7 +4459,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4465,14 +4469,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4482,14 +4486,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4506,7 +4510,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4516,14 +4520,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4540,7 +4544,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4550,14 +4554,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4574,7 +4578,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4584,14 +4588,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4601,14 +4605,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4618,14 +4622,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4642,7 +4646,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4669,14 +4673,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4686,14 +4690,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4710,7 +4714,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4727,7 +4731,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4737,14 +4741,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4754,14 +4758,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4778,7 +4782,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4788,14 +4792,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4812,7 +4816,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4829,7 +4833,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4846,7 +4850,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4863,7 +4867,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4880,7 +4884,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4890,14 +4894,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4924,14 +4928,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4948,7 +4952,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4965,7 +4969,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4982,7 +4986,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4992,14 +4996,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5016,7 +5020,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5033,7 +5037,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5050,7 +5054,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5077,14 +5081,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5101,7 +5105,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5111,14 +5115,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5135,7 +5139,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5152,7 +5156,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5169,7 +5173,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5186,7 +5190,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5203,7 +5207,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5220,7 +5224,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5230,14 +5234,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5254,7 +5258,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5271,7 +5275,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5288,7 +5292,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5305,7 +5309,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5322,7 +5326,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5339,7 +5343,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5356,7 +5360,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5366,14 +5370,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5390,7 +5394,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5407,7 +5411,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5424,7 +5428,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5441,7 +5445,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5458,7 +5462,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5475,7 +5479,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5492,7 +5496,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5509,7 +5513,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5526,7 +5530,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5543,7 +5547,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5560,7 +5564,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5577,7 +5581,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5594,7 +5598,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5611,7 +5615,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5621,14 +5625,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5645,7 +5649,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5655,14 +5659,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5679,7 +5683,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5689,14 +5693,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5713,7 +5717,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5730,7 +5734,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5747,7 +5751,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5764,7 +5768,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5774,14 +5778,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5798,7 +5802,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5815,7 +5819,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5832,7 +5836,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5842,14 +5846,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5866,7 +5870,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5904,894 +5908,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Alerion Clean Power S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Altea Green Power S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Aquafil S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CEMBRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CY4Gate S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DIGITAL BROS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DiaSorin S.p.A</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ENAV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ENEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ENEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>EQUITA GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Energy Time S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>F.I.L.A. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>FINCANTIERI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>FNM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>First Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>GEFRAN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>IGD SIIQ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>IMMSI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>LU-VE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>LU-VE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Orsero S.p.A.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>PHILOGEN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>PININFARINA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Poste Italiane S.p.A.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>REPLY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>SOL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>SYS-DAT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>TERNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>TERNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>The Italian Sea Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Toscana Aeroporti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Unicredit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Unicredit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Unipol S.p.A.</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>WEBUILD S.p.A.</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>